--- a/july 2026/LMT_JULY_26/Nagina Food.xlsx
+++ b/july 2026/LMT_JULY_26/Nagina Food.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FED2857-5422-49F9-9DD0-50C752086B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CCF488-522C-42C0-97A0-B7C4C51EC39E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3236,7 +3236,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -3264,7 +3264,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -4457,7 +4457,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -4485,7 +4485,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -5678,7 +5678,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -5706,7 +5706,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -6899,7 +6899,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -6927,7 +6927,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -8120,7 +8120,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -8148,7 +8148,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -9341,7 +9341,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -9369,7 +9369,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -10559,7 +10559,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -10587,7 +10587,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -11776,7 +11776,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -11804,7 +11804,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -12993,7 +12993,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -13021,7 +13021,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -14210,7 +14210,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -14238,7 +14238,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -18177,7 +18177,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -18205,7 +18205,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -19394,7 +19394,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -19422,7 +19422,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -20611,7 +20611,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -20639,7 +20639,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -21828,7 +21828,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -21856,7 +21856,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -23050,7 +23050,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -23078,7 +23078,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -24634,8 +24634,7 @@
       <c r="L4" s="212"/>
       <c r="M4" s="212"/>
       <c r="N4" s="213">
-        <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -24662,8 +24661,8 @@
       <c r="L5" s="212"/>
       <c r="M5" s="212"/>
       <c r="N5" s="213">
-        <f ca="1">N4-1</f>
-        <v>46219</v>
+        <f>N4-1</f>
+        <v>46215</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -25795,6 +25794,7 @@
       <c r="F27" s="150"/>
       <c r="G27" s="151"/>
       <c r="H27" s="151"/>
+      <c r="P27" s="108"/>
     </row>
     <row r="28" spans="1:26 16384:16384" x14ac:dyDescent="0.35">
       <c r="B28" s="239" t="s">
@@ -26138,7 +26138,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -26166,7 +26166,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -27359,7 +27359,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -27387,7 +27387,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -28579,7 +28579,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -28607,7 +28607,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -29800,7 +29800,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -29828,7 +29828,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
@@ -31021,7 +31021,7 @@
       <c r="M4" s="212"/>
       <c r="N4" s="213">
         <f ca="1">TODAY()</f>
-        <v>46220</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="213"/>
       <c r="P4" s="213"/>
@@ -31049,7 +31049,7 @@
       <c r="M5" s="212"/>
       <c r="N5" s="213">
         <f ca="1">N4-1</f>
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="211"/>
       <c r="P5" s="211"/>
